--- a/AAII_Financials/Yearly/COMM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/COMM_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
   <si>
     <t>COMM</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>9228100</v>
+        <v>5789200</v>
       </c>
       <c r="E8" s="3">
-        <v>8586700</v>
+        <v>7524700</v>
       </c>
       <c r="F8" s="3">
+        <v>6737400</v>
+      </c>
+      <c r="G8" s="3">
         <v>8435900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8345100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4568500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4560600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4923600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3807800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3829600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3480100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3321900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3275500</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>6424000</v>
+        <v>3640900</v>
       </c>
       <c r="E9" s="3">
-        <v>5902400</v>
+        <v>4930700</v>
       </c>
       <c r="F9" s="3">
+        <v>4297800</v>
+      </c>
+      <c r="G9" s="3">
         <v>5688100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5941000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5815400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5647900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2894400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2462000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2432300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2279200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2261200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2444600</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2804100</v>
+        <v>2148300</v>
       </c>
       <c r="E10" s="3">
-        <v>2684300</v>
+        <v>2594000</v>
       </c>
       <c r="F10" s="3">
+        <v>2439600</v>
+      </c>
+      <c r="G10" s="3">
         <v>2747800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2404100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-1246900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-1087300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2029300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1345800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1397300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1200900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1060700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>830900</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,50 +873,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>657400</v>
+        <v>459700</v>
       </c>
       <c r="E12" s="3">
-        <v>683200</v>
+        <v>543600</v>
       </c>
       <c r="F12" s="3">
+        <v>565000</v>
+      </c>
+      <c r="G12" s="3">
         <v>703300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>578500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>185700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>185600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>201300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>136000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>125300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>126400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>121700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>118200</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -944,93 +960,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>1220700</v>
+        <v>628200</v>
       </c>
       <c r="E14" s="3">
-        <v>195900</v>
+        <v>1217700</v>
       </c>
       <c r="F14" s="3">
+        <v>135700</v>
+      </c>
+      <c r="G14" s="3">
         <v>320000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>659100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>78500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>91800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>143700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>120300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>43500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>67600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>63900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>144800</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>543000</v>
+        <v>327100</v>
       </c>
       <c r="E15" s="3">
-        <v>613000</v>
+        <v>440000</v>
       </c>
       <c r="F15" s="3">
+        <v>510000</v>
+      </c>
+      <c r="G15" s="3">
         <v>630500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>593200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>264600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>271000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>297200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>220600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>178300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>174900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>175700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>174800</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>9941900</v>
+        <v>5902100</v>
       </c>
       <c r="E17" s="3">
-        <v>8538100</v>
+        <v>8137800</v>
       </c>
       <c r="F17" s="3">
+        <v>6540800</v>
+      </c>
+      <c r="G17" s="3">
         <v>8487700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8853600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4118500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4088600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4356000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3626200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3252200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3150400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3083600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3463900</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-713800</v>
+        <v>-112900</v>
       </c>
       <c r="E18" s="3">
-        <v>48600</v>
+        <v>-613100</v>
       </c>
       <c r="F18" s="3">
+        <v>196600</v>
+      </c>
+      <c r="G18" s="3">
         <v>-51800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-508500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>450000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>472000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>567600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>181600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>577400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>329700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>238200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-188400</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>2700</v>
+        <v>70800</v>
       </c>
       <c r="E20" s="3">
-        <v>-21900</v>
+        <v>2300</v>
       </c>
       <c r="F20" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="G20" s="3">
         <v>-24900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>11700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-37300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-17500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-8900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-81500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-44900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-12000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-50500</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-15000</v>
+        <v>519100</v>
       </c>
       <c r="E21" s="3">
-        <v>813000</v>
+        <v>85300</v>
       </c>
       <c r="F21" s="3">
+        <v>958300</v>
+      </c>
+      <c r="G21" s="3">
         <v>746600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>274100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>770200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>844800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>949200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>476200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>755500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>541400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>488600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>58100</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>675800</v>
+      </c>
+      <c r="E22" s="3">
         <v>588900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>561200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>577800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>577200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>242000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>257000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>277500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>234700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>178900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>208600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>189000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>263800</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>-1300000</v>
+        <v>-717900</v>
       </c>
       <c r="E23" s="3">
-        <v>-534500</v>
+        <v>-1199700</v>
       </c>
       <c r="F23" s="3">
+        <v>-389200</v>
+      </c>
+      <c r="G23" s="3">
         <v>-654500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1074000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>170700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>209800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>272600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-62000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>317100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>76200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>37300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-502800</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>-13100</v>
+        <v>133400</v>
       </c>
       <c r="E24" s="3">
-        <v>-71900</v>
+        <v>-15000</v>
       </c>
       <c r="F24" s="3">
+        <v>-39200</v>
+      </c>
+      <c r="G24" s="3">
         <v>-81100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-146100</v>
-      </c>
-      <c r="H24" s="3">
-        <v>38300</v>
       </c>
       <c r="I24" s="3">
         <v>38300</v>
       </c>
       <c r="J24" s="3">
+        <v>38300</v>
+      </c>
+      <c r="K24" s="3">
         <v>49700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>8900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>80300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>56800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>31900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-110400</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>-1286900</v>
+        <v>-851300</v>
       </c>
       <c r="E26" s="3">
-        <v>-462600</v>
+        <v>-1184700</v>
       </c>
       <c r="F26" s="3">
+        <v>-350000</v>
+      </c>
+      <c r="G26" s="3">
         <v>-573400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-927900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>132400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>171500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>222800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-70900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>236800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>19400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-392400</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>-1345900</v>
+        <v>-913100</v>
       </c>
       <c r="E27" s="3">
-        <v>-519900</v>
+        <v>-1243700</v>
       </c>
       <c r="F27" s="3">
+        <v>-407300</v>
+      </c>
+      <c r="G27" s="3">
         <v>-629500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-971600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>132400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>171500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>222800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-70900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>236800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-392400</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1523,32 +1580,35 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="3">
+        <v>-599600</v>
+      </c>
+      <c r="E29" s="3">
+        <v>-102200</v>
+      </c>
+      <c r="F29" s="3">
+        <v>-112600</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-1600</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>7800</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>22300</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>24</v>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2700</v>
+        <v>-70800</v>
       </c>
       <c r="E32" s="3">
-        <v>21900</v>
+        <v>-2300</v>
       </c>
       <c r="F32" s="3">
+        <v>24600</v>
+      </c>
+      <c r="G32" s="3">
         <v>24900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-11700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>37300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>17500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>8900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>81500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>44900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>12000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>50500</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1512700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1345900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-519900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-629500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-973200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>140200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>193800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>222800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-70900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>236800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-392400</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1512700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1345900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-519900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-629500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-973200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>140200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>193800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>222800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-70900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>236800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-392400</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,50 +1986,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>543800</v>
+      </c>
+      <c r="E41" s="3">
         <v>398100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>360300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>521900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>598200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>458200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>454000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>428200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>562900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>729300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>346300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>264400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>317100</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1984,177 +2073,192 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>815200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1523600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1532600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1487400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1698800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>810400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>898800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>952400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>833000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>612000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>607500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>596100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>581800</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1079700</v>
+      </c>
+      <c r="E44" s="3">
         <v>1588100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1435800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1088900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>975900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>473300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>444900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>473300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>441800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>367200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>372200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>312000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>338100</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>424000</v>
+      </c>
+      <c r="E45" s="3">
         <v>216400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>251000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>256300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>238900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>135900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>146100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>139900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>166900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>119100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>127400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>114900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>130400</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2862700</v>
+      </c>
+      <c r="E46" s="3">
         <v>3726200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3579700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3354500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3511800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1877800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1943900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1993800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2004600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1827600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1453400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1287300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1367300</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2186,101 +2290,110 @@
         <v>0</v>
       </c>
       <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
         <v>3100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7200</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>657800</v>
+      </c>
+      <c r="E48" s="3">
         <v>758600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>818800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>843800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>946700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>450900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>467300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>475000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>528700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>786100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>620300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>355200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>407600</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5097100</v>
+      </c>
+      <c r="E49" s="3">
         <v>6545900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8259000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8936900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9735300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4204300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4522700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4567400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4838100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3973700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4294900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3052600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3267500</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>754300</v>
+      </c>
+      <c r="E52" s="3">
         <v>654700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>602000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>441600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>237800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>97600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>107800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>105900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>131200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>87300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>192500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>93700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>103600</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9371900</v>
+      </c>
+      <c r="E54" s="3">
         <v>11685400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13259500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13576800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14431600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6630500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7041700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7142000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7502600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4917100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4734100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4793300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5153200</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,50 +2654,54 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>435900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1025500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1160700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1010800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1148000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>399200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>436700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>415900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>300800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>177800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>251600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>194300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>180700</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2584,201 +2717,216 @@
       <c r="G58" s="3">
         <v>32000</v>
       </c>
-      <c r="H58" s="3" t="s">
+      <c r="H58" s="3">
+        <v>32000</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
-        <v>12500</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>12500</v>
       </c>
       <c r="L58" s="3">
+        <v>12500</v>
+      </c>
+      <c r="M58" s="3">
         <v>9000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12300</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>941500</v>
+      </c>
+      <c r="E59" s="3">
         <v>1050000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>989800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>910600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>862000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>291400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>287000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>429400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>371700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>289000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>332300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>344500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>320600</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1409400</v>
+      </c>
+      <c r="E60" s="3">
         <v>2107500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2182500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1953400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2042000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>690600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>723700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>857800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>685100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>475800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>593400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>549600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>513700</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9246600</v>
+      </c>
+      <c r="E61" s="3">
         <v>9469600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9478500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9488600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9800400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3985900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4369400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4549500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5231100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2659900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2505100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2460000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2550700</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>522600</v>
+      </c>
+      <c r="E62" s="3">
         <v>554000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>699000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>738000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>752900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>197200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>300700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>340600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>363700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>473700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>934100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>601400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>723700</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11178600</v>
+      </c>
+      <c r="E66" s="3">
         <v>12131100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12360000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12180000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12595300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4873800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5393800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5747900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6279900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3609400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3646000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3611000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3788100</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,27 +3210,30 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1162100</v>
+      </c>
+      <c r="E70" s="3">
         <v>1100300</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>1056100</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>1041800</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>1000000</v>
       </c>
-      <c r="H70" s="3">
-        <v>0</v>
-      </c>
       <c r="I70" s="3">
         <v>0</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-4953100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3502200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2215300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1752700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1179300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-249800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-396000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-589600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-812400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-741500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-978300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-447700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-252300</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2968800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1546000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-156600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>355000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>836300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1756800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1647800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1394100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1222700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1307600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1088000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1182300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1365100</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1512700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1345900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-519900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-629500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-973200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>140200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>193800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>222800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-70900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>236800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-392400</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>561200</v>
+      </c>
+      <c r="E83" s="3">
         <v>696100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>786300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>823300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>770900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>357500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>378000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>399100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>303500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>259500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>256600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>262300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>297000</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>289900</v>
+      </c>
+      <c r="E89" s="3">
         <v>190000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>122300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>436200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>596400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>494100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>586300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>640200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>327100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>289400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>237700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>286100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>131000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-53300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-101300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-131400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-121200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-104100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-82300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-68700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-68300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-56500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-36900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-36800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-28000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-39500</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-82100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-136800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-120200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5154900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-64300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-166200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-54600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3050600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-76000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-63400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-35500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3171500</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,26 +4220,27 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>-14900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-43000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-14300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-43700</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
@@ -4021,17 +4254,20 @@
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-538700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-200000</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-181700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-65000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-139500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-383800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4698600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-409600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-413600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-708400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2578100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>190800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-89700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-299500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2655300</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-7600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-16000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>19300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-11900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-21000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-21300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2700</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-3800</v>
       </c>
       <c r="O101" s="3">
         <v>-3800</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>145700</v>
+      </c>
+      <c r="E102" s="3">
         <v>37800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-161600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-76300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>140000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>25700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-134700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-166400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>383000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>81900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-52700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-389000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/COMM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/COMM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
   <si>
     <t>COMM</t>
   </si>
@@ -783,13 +783,13 @@
         <v>5688100</v>
       </c>
       <c r="H9" s="3">
-        <v>5941000</v>
+        <v>5722200</v>
       </c>
       <c r="I9" s="3">
-        <v>5815400</v>
+        <v>2935200</v>
       </c>
       <c r="J9" s="3">
-        <v>5647900</v>
+        <v>2855100</v>
       </c>
       <c r="K9" s="3">
         <v>2894400</v>
@@ -828,13 +828,13 @@
         <v>2747800</v>
       </c>
       <c r="H10" s="3">
-        <v>2404100</v>
+        <v>2622900</v>
       </c>
       <c r="I10" s="3">
-        <v>-1246900</v>
+        <v>1633300</v>
       </c>
       <c r="J10" s="3">
-        <v>-1087300</v>
+        <v>1705500</v>
       </c>
       <c r="K10" s="3">
         <v>2029300</v>
@@ -970,7 +970,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>628200</v>
+        <v>559400</v>
       </c>
       <c r="E14" s="3">
         <v>1217700</v>
@@ -979,16 +979,16 @@
         <v>135700</v>
       </c>
       <c r="G14" s="3">
-        <v>320000</v>
+        <v>337900</v>
       </c>
       <c r="H14" s="3">
-        <v>659100</v>
+        <v>682600</v>
       </c>
       <c r="I14" s="3">
-        <v>78500</v>
+        <v>93500</v>
       </c>
       <c r="J14" s="3">
-        <v>91800</v>
+        <v>43800</v>
       </c>
       <c r="K14" s="3">
         <v>143700</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>5902100</v>
+        <v>5270900</v>
       </c>
       <c r="E17" s="3">
-        <v>8137800</v>
+        <v>6921000</v>
       </c>
       <c r="F17" s="3">
-        <v>6540800</v>
+        <v>6401600</v>
       </c>
       <c r="G17" s="3">
-        <v>8487700</v>
+        <v>8167900</v>
       </c>
       <c r="H17" s="3">
-        <v>8853600</v>
+        <v>8171300</v>
       </c>
       <c r="I17" s="3">
-        <v>4118500</v>
+        <v>4057800</v>
       </c>
       <c r="J17" s="3">
-        <v>4088600</v>
+        <v>4043800</v>
       </c>
       <c r="K17" s="3">
         <v>4356000</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-112900</v>
+        <v>518300</v>
       </c>
       <c r="E18" s="3">
-        <v>-613100</v>
+        <v>603700</v>
       </c>
       <c r="F18" s="3">
-        <v>196600</v>
+        <v>335800</v>
       </c>
       <c r="G18" s="3">
-        <v>-51800</v>
+        <v>268000</v>
       </c>
       <c r="H18" s="3">
-        <v>-508500</v>
+        <v>173800</v>
       </c>
       <c r="I18" s="3">
-        <v>450000</v>
+        <v>510700</v>
       </c>
       <c r="J18" s="3">
-        <v>472000</v>
+        <v>516800</v>
       </c>
       <c r="K18" s="3">
         <v>567600</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>70800</v>
+        <v>12100</v>
       </c>
       <c r="E20" s="3">
-        <v>2300</v>
+        <v>-400</v>
       </c>
       <c r="F20" s="3">
-        <v>-24600</v>
+        <v>30000</v>
       </c>
       <c r="G20" s="3">
-        <v>-24900</v>
+        <v>11200</v>
       </c>
       <c r="H20" s="3">
-        <v>11700</v>
+        <v>6100</v>
       </c>
       <c r="I20" s="3">
-        <v>-37300</v>
+        <v>11500</v>
       </c>
       <c r="J20" s="3">
-        <v>-5200</v>
+        <v>10400</v>
       </c>
       <c r="K20" s="3">
         <v>-17500</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>519100</v>
+        <v>833300</v>
       </c>
       <c r="E21" s="3">
-        <v>85300</v>
+        <v>1044100</v>
       </c>
       <c r="F21" s="3">
-        <v>958300</v>
+        <v>815800</v>
       </c>
       <c r="G21" s="3">
-        <v>746600</v>
+        <v>887300</v>
       </c>
       <c r="H21" s="3">
-        <v>274100</v>
+        <v>760900</v>
       </c>
       <c r="I21" s="3">
-        <v>770200</v>
+        <v>763800</v>
       </c>
       <c r="J21" s="3">
-        <v>844800</v>
+        <v>777400</v>
       </c>
       <c r="K21" s="3">
         <v>949200</v>
@@ -1377,13 +1377,13 @@
         <v>-81100</v>
       </c>
       <c r="H24" s="3">
-        <v>-146100</v>
+        <v>-144500</v>
       </c>
       <c r="I24" s="3">
-        <v>38300</v>
+        <v>30500</v>
       </c>
       <c r="J24" s="3">
-        <v>38300</v>
+        <v>16000</v>
       </c>
       <c r="K24" s="3">
         <v>49700</v>
@@ -1467,13 +1467,13 @@
         <v>-573400</v>
       </c>
       <c r="H26" s="3">
-        <v>-927900</v>
+        <v>-929500</v>
       </c>
       <c r="I26" s="3">
-        <v>132400</v>
+        <v>140200</v>
       </c>
       <c r="J26" s="3">
-        <v>171500</v>
+        <v>193800</v>
       </c>
       <c r="K26" s="3">
         <v>222800</v>
@@ -1500,25 +1500,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>-913100</v>
+        <v>-1512700</v>
       </c>
       <c r="E27" s="3">
-        <v>-1243700</v>
+        <v>-1345900</v>
       </c>
       <c r="F27" s="3">
-        <v>-407300</v>
+        <v>-519900</v>
       </c>
       <c r="G27" s="3">
         <v>-629500</v>
       </c>
       <c r="H27" s="3">
-        <v>-971600</v>
+        <v>-973200</v>
       </c>
       <c r="I27" s="3">
-        <v>132400</v>
+        <v>140200</v>
       </c>
       <c r="J27" s="3">
-        <v>171500</v>
+        <v>193800</v>
       </c>
       <c r="K27" s="3">
         <v>222800</v>
@@ -1598,17 +1598,17 @@
       <c r="F29" s="3">
         <v>-112600</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>24</v>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>-1600</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>7800</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>22300</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>24</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-70800</v>
+        <v>-12100</v>
       </c>
       <c r="E32" s="3">
-        <v>-2300</v>
+        <v>400</v>
       </c>
       <c r="F32" s="3">
-        <v>24600</v>
+        <v>-30000</v>
       </c>
       <c r="G32" s="3">
-        <v>24900</v>
+        <v>-11200</v>
       </c>
       <c r="H32" s="3">
-        <v>-11700</v>
+        <v>-6100</v>
       </c>
       <c r="I32" s="3">
-        <v>37300</v>
+        <v>-11500</v>
       </c>
       <c r="J32" s="3">
-        <v>5200</v>
+        <v>-10400</v>
       </c>
       <c r="K32" s="3">
         <v>17500</v>
@@ -1770,19 +1770,19 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-1512700</v>
+        <v>-1450900</v>
       </c>
       <c r="E33" s="3">
-        <v>-1345900</v>
+        <v>-1286900</v>
       </c>
       <c r="F33" s="3">
-        <v>-519900</v>
+        <v>-462600</v>
       </c>
       <c r="G33" s="3">
-        <v>-629500</v>
+        <v>-573400</v>
       </c>
       <c r="H33" s="3">
-        <v>-973200</v>
+        <v>-929500</v>
       </c>
       <c r="I33" s="3">
         <v>140200</v>
@@ -1860,19 +1860,19 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-1512700</v>
+        <v>-1450900</v>
       </c>
       <c r="E35" s="3">
-        <v>-1345900</v>
+        <v>-1286900</v>
       </c>
       <c r="F35" s="3">
-        <v>-519900</v>
+        <v>-462600</v>
       </c>
       <c r="G35" s="3">
-        <v>-629500</v>
+        <v>-573400</v>
       </c>
       <c r="H35" s="3">
-        <v>-973200</v>
+        <v>-929500</v>
       </c>
       <c r="I35" s="3">
         <v>140200</v>
@@ -1996,7 +1996,7 @@
         <v>543800</v>
       </c>
       <c r="E41" s="3">
-        <v>398100</v>
+        <v>373000</v>
       </c>
       <c r="F41" s="3">
         <v>360300</v>
@@ -2086,7 +2086,7 @@
         <v>815200</v>
       </c>
       <c r="E43" s="3">
-        <v>1523600</v>
+        <v>1178200</v>
       </c>
       <c r="F43" s="3">
         <v>1532600</v>
@@ -2131,7 +2131,7 @@
         <v>1079700</v>
       </c>
       <c r="E44" s="3">
-        <v>1588100</v>
+        <v>1376000</v>
       </c>
       <c r="F44" s="3">
         <v>1435800</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>424000</v>
+        <v>287300</v>
       </c>
       <c r="E45" s="3">
-        <v>216400</v>
+        <v>631700</v>
       </c>
       <c r="F45" s="3">
-        <v>251000</v>
+        <v>5700</v>
       </c>
       <c r="G45" s="3">
-        <v>256300</v>
+        <v>11700</v>
       </c>
       <c r="H45" s="3">
-        <v>238900</v>
+        <v>4900</v>
       </c>
       <c r="I45" s="3">
-        <v>135900</v>
+        <v>2500</v>
       </c>
       <c r="J45" s="3">
-        <v>146100</v>
+        <v>9100</v>
       </c>
       <c r="K45" s="3">
         <v>139900</v>
@@ -2221,7 +2221,7 @@
         <v>2862700</v>
       </c>
       <c r="E46" s="3">
-        <v>3726200</v>
+        <v>3726100</v>
       </c>
       <c r="F46" s="3">
         <v>3579700</v>
@@ -2262,26 +2262,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>8600</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2311,7 +2311,7 @@
         <v>657800</v>
       </c>
       <c r="E48" s="3">
-        <v>758600</v>
+        <v>742900</v>
       </c>
       <c r="F48" s="3">
         <v>818800</v>
@@ -2320,7 +2320,7 @@
         <v>843800</v>
       </c>
       <c r="H48" s="3">
-        <v>946700</v>
+        <v>928700</v>
       </c>
       <c r="I48" s="3">
         <v>450900</v>
@@ -2356,7 +2356,7 @@
         <v>5097100</v>
       </c>
       <c r="E49" s="3">
-        <v>6545900</v>
+        <v>5987500</v>
       </c>
       <c r="F49" s="3">
         <v>8259000</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>754300</v>
+        <v>138700</v>
       </c>
       <c r="E52" s="3">
-        <v>654700</v>
+        <v>725700</v>
       </c>
       <c r="F52" s="3">
-        <v>602000</v>
+        <v>174900</v>
       </c>
       <c r="G52" s="3">
-        <v>441600</v>
+        <v>153500</v>
       </c>
       <c r="H52" s="3">
-        <v>237800</v>
+        <v>152700</v>
       </c>
       <c r="I52" s="3">
-        <v>97600</v>
+        <v>54700</v>
       </c>
       <c r="J52" s="3">
-        <v>107800</v>
+        <v>61900</v>
       </c>
       <c r="K52" s="3">
         <v>105900</v>
@@ -2664,7 +2664,7 @@
         <v>435900</v>
       </c>
       <c r="E57" s="3">
-        <v>1025500</v>
+        <v>684300</v>
       </c>
       <c r="F57" s="3">
         <v>1160700</v>
@@ -2706,22 +2706,22 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>32000</v>
+        <v>68500</v>
       </c>
       <c r="E58" s="3">
-        <v>32000</v>
+        <v>76400</v>
       </c>
       <c r="F58" s="3">
-        <v>32000</v>
+        <v>80200</v>
       </c>
       <c r="G58" s="3">
-        <v>32000</v>
+        <v>94400</v>
       </c>
       <c r="H58" s="3">
-        <v>32000</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>24</v>
+        <v>93700</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>941500</v>
+        <v>613200</v>
       </c>
       <c r="E59" s="3">
-        <v>1050000</v>
+        <v>942800</v>
       </c>
       <c r="F59" s="3">
-        <v>989800</v>
+        <v>518600</v>
       </c>
       <c r="G59" s="3">
-        <v>910600</v>
+        <v>450100</v>
       </c>
       <c r="H59" s="3">
-        <v>862000</v>
+        <v>424000</v>
       </c>
       <c r="I59" s="3">
-        <v>291400</v>
+        <v>145700</v>
       </c>
       <c r="J59" s="3">
-        <v>287000</v>
+        <v>74500</v>
       </c>
       <c r="K59" s="3">
         <v>429400</v>
@@ -2841,19 +2841,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>9246600</v>
+        <v>9394500</v>
       </c>
       <c r="E61" s="3">
-        <v>9469600</v>
+        <v>9589000</v>
       </c>
       <c r="F61" s="3">
-        <v>9478500</v>
+        <v>9629600</v>
       </c>
       <c r="G61" s="3">
-        <v>9488600</v>
+        <v>9637600</v>
       </c>
       <c r="H61" s="3">
-        <v>9800400</v>
+        <v>9977100</v>
       </c>
       <c r="I61" s="3">
         <v>3985900</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>522600</v>
+        <v>168400</v>
       </c>
       <c r="E62" s="3">
-        <v>554000</v>
+        <v>238200</v>
       </c>
       <c r="F62" s="3">
-        <v>699000</v>
+        <v>244800</v>
       </c>
       <c r="G62" s="3">
-        <v>738000</v>
+        <v>282500</v>
       </c>
       <c r="H62" s="3">
-        <v>752900</v>
+        <v>286300</v>
       </c>
       <c r="I62" s="3">
-        <v>197200</v>
+        <v>100600</v>
       </c>
       <c r="J62" s="3">
-        <v>300700</v>
+        <v>141300</v>
       </c>
       <c r="K62" s="3">
         <v>340600</v>
@@ -3081,7 +3081,7 @@
         <v>12595300</v>
       </c>
       <c r="I66" s="3">
-        <v>4873800</v>
+        <v>4873700</v>
       </c>
       <c r="J66" s="3">
         <v>5393800</v>
@@ -3630,19 +3630,19 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-1512700</v>
+        <v>-1450900</v>
       </c>
       <c r="E81" s="3">
-        <v>-1345900</v>
+        <v>-1286900</v>
       </c>
       <c r="F81" s="3">
-        <v>-519900</v>
+        <v>-462600</v>
       </c>
       <c r="G81" s="3">
-        <v>-629500</v>
+        <v>-573400</v>
       </c>
       <c r="H81" s="3">
-        <v>-973200</v>
+        <v>-929500</v>
       </c>
       <c r="I81" s="3">
         <v>140200</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>561200</v>
+        <v>234100</v>
       </c>
       <c r="E83" s="3">
-        <v>696100</v>
+        <v>256100</v>
       </c>
       <c r="F83" s="3">
-        <v>786300</v>
+        <v>276300</v>
       </c>
       <c r="G83" s="3">
-        <v>823300</v>
+        <v>192800</v>
       </c>
       <c r="H83" s="3">
-        <v>770900</v>
+        <v>177700</v>
       </c>
       <c r="I83" s="3">
-        <v>357500</v>
+        <v>92900</v>
       </c>
       <c r="J83" s="3">
-        <v>378000</v>
+        <v>107000</v>
       </c>
       <c r="K83" s="3">
         <v>399100</v>
@@ -4230,16 +4230,16 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-14900</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-43000</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-14300</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-43700</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -4425,7 +4425,7 @@
         <v>-409600</v>
       </c>
       <c r="J100" s="3">
-        <v>-413600</v>
+        <v>-413700</v>
       </c>
       <c r="K100" s="3">
         <v>-708400</v>
@@ -4470,7 +4470,7 @@
         <v>-16000</v>
       </c>
       <c r="J101" s="3">
-        <v>19300</v>
+        <v>19400</v>
       </c>
       <c r="K101" s="3">
         <v>-11900</v>
@@ -4515,7 +4515,7 @@
         <v>4200</v>
       </c>
       <c r="J102" s="3">
-        <v>25700</v>
+        <v>25800</v>
       </c>
       <c r="K102" s="3">
         <v>-134700</v>

--- a/AAII_Financials/Yearly/COMM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/COMM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
   <si>
     <t>COMM</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>5789200</v>
+        <v>4205800</v>
       </c>
       <c r="E8" s="3">
-        <v>7524700</v>
+        <v>4565200</v>
       </c>
       <c r="F8" s="3">
+        <v>5788800</v>
+      </c>
+      <c r="G8" s="3">
         <v>6737400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8435900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8345100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4568500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4560600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4923600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3807800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3829600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3480100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3321900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3275500</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3640900</v>
+        <v>2628900</v>
       </c>
       <c r="E9" s="3">
-        <v>4930700</v>
+        <v>2901000</v>
       </c>
       <c r="F9" s="3">
+        <v>3803200</v>
+      </c>
+      <c r="G9" s="3">
         <v>4297800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5688100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5722200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2935200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2855100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2894400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2462000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2432300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2279200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2261200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2444600</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2148300</v>
+        <v>1576900</v>
       </c>
       <c r="E10" s="3">
-        <v>2594000</v>
+        <v>1664200</v>
       </c>
       <c r="F10" s="3">
+        <v>1985600</v>
+      </c>
+      <c r="G10" s="3">
         <v>2439600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2747800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2622900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1633300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1705500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2029300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1345800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1397300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1200900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1060700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>830900</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,53 +886,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>459700</v>
+        <v>316200</v>
       </c>
       <c r="E12" s="3">
-        <v>543600</v>
+        <v>383100</v>
       </c>
       <c r="F12" s="3">
+        <v>451600</v>
+      </c>
+      <c r="G12" s="3">
         <v>565000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>703300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>578500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>185700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>185600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>201300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>136000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>125300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>126400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>121700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>118200</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -963,99 +979,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>559400</v>
+        <v>106500</v>
       </c>
       <c r="E14" s="3">
-        <v>1217700</v>
+        <v>549300</v>
       </c>
       <c r="F14" s="3">
+        <v>1196500</v>
+      </c>
+      <c r="G14" s="3">
         <v>135700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>337900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>682600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>93500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>43800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>143700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>120300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>43500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>67600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>63900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>144800</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>327100</v>
+        <v>236500</v>
       </c>
       <c r="E15" s="3">
-        <v>440000</v>
+        <v>301000</v>
       </c>
       <c r="F15" s="3">
+        <v>400100</v>
+      </c>
+      <c r="G15" s="3">
         <v>510000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>630500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>593200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>264600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>271000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>297200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>220600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>178300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>174900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>175700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>174800</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>5270900</v>
+        <v>3847200</v>
       </c>
       <c r="E17" s="3">
-        <v>6921000</v>
+        <v>4343700</v>
       </c>
       <c r="F17" s="3">
+        <v>5528500</v>
+      </c>
+      <c r="G17" s="3">
         <v>6401600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8167900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8171300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4057800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4043800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4356000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3626200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3252200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3150400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3083600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3463900</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>518300</v>
+        <v>358600</v>
       </c>
       <c r="E18" s="3">
-        <v>603700</v>
+        <v>221500</v>
       </c>
       <c r="F18" s="3">
+        <v>260300</v>
+      </c>
+      <c r="G18" s="3">
         <v>335800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>268000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>173800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>510700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>516800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>567600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>181600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>577400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>329700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>238200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-188400</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>12100</v>
+        <v>-14600</v>
       </c>
       <c r="E20" s="3">
-        <v>-400</v>
+        <v>5900</v>
       </c>
       <c r="F20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G20" s="3">
         <v>30000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>11200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>11500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>10400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-17500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-81500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-44900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-12000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-50500</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>833300</v>
+        <v>609700</v>
       </c>
       <c r="E21" s="3">
-        <v>1044100</v>
+        <v>516600</v>
       </c>
       <c r="F21" s="3">
+        <v>661300</v>
+      </c>
+      <c r="G21" s="3">
         <v>815800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>887300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>760900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>763800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>777400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>949200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>476200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>755500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>541400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>488600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>58100</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>686900</v>
+      </c>
+      <c r="E22" s="3">
         <v>675800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>588900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>561200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>577800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>577200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>242000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>257000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>277500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>234700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>178900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>208600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>189000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>263800</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>-717900</v>
+        <v>-409300</v>
       </c>
       <c r="E23" s="3">
-        <v>-1199700</v>
+        <v>-998400</v>
       </c>
       <c r="F23" s="3">
+        <v>-1521400</v>
+      </c>
+      <c r="G23" s="3">
         <v>-389200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-654500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1074000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>170700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>209800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>272600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-62000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>317100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>76200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>37300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-502800</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>133400</v>
+        <v>51700</v>
       </c>
       <c r="E24" s="3">
-        <v>-15000</v>
+        <v>97400</v>
       </c>
       <c r="F24" s="3">
+        <v>-91300</v>
+      </c>
+      <c r="G24" s="3">
         <v>-39200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-81100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-144500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>30500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>16000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>49700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>80300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>56800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>31900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-110400</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>-851300</v>
+        <v>-461000</v>
       </c>
       <c r="E26" s="3">
-        <v>-1184700</v>
+        <v>-1095800</v>
       </c>
       <c r="F26" s="3">
+        <v>-1430100</v>
+      </c>
+      <c r="G26" s="3">
         <v>-350000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-573400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-929500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>140200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>193800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>222800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-70900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>236800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>19400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-392400</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>-1512700</v>
+        <v>-380700</v>
       </c>
       <c r="E27" s="3">
+        <v>-1568600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1345900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-519900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-629500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-973200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>140200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>193800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>222800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-70900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>236800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-392400</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1583,24 +1640,27 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
-        <v>-599600</v>
+        <v>145500</v>
       </c>
       <c r="E29" s="3">
-        <v>-102200</v>
+        <v>-411000</v>
       </c>
       <c r="F29" s="3">
+        <v>143200</v>
+      </c>
+      <c r="G29" s="3">
         <v>-112600</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
@@ -1610,8 +1670,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>24</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>24</v>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-12100</v>
+        <v>14600</v>
       </c>
       <c r="E32" s="3">
-        <v>400</v>
+        <v>-5900</v>
       </c>
       <c r="F32" s="3">
+        <v>900</v>
+      </c>
+      <c r="G32" s="3">
         <v>-30000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-11200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-11500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-10400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>17500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>81500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>44900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>12000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>50500</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-1450900</v>
+        <v>-315500</v>
       </c>
       <c r="E33" s="3">
+        <v>-1506800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1286900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-462600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-573400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-929500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>140200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>193800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>222800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-70900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>236800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-392400</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-1450900</v>
+        <v>-315500</v>
       </c>
       <c r="E35" s="3">
+        <v>-1506800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1286900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-462600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-573400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-929500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>140200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>193800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>222800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-70900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>236800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-392400</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,53 +2072,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>543800</v>
+        <v>564900</v>
       </c>
       <c r="E41" s="3">
+        <v>500300</v>
+      </c>
+      <c r="F41" s="3">
         <v>373000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>360300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>521900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>598200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>458200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>454000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>428200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>562900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>729300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>346300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>264400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>317100</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2076,200 +2165,215 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>815200</v>
+        <v>685900</v>
       </c>
       <c r="E43" s="3">
+        <v>581900</v>
+      </c>
+      <c r="F43" s="3">
         <v>1178200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1532600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1487400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1698800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>810400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>898800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>952400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>833000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>612000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>607500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>596100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>581800</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1079700</v>
+        <v>736800</v>
       </c>
       <c r="E44" s="3">
+        <v>900800</v>
+      </c>
+      <c r="F44" s="3">
         <v>1376000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1435800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1088900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>975900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>473300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>444900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>473300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>441800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>367200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>372200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>312000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>338100</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>287300</v>
+        <v>1357500</v>
       </c>
       <c r="E45" s="3">
+        <v>716700</v>
+      </c>
+      <c r="F45" s="3">
         <v>631700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>139900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>166900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>119100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>127400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>114900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>130400</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2862700</v>
+        <v>3484500</v>
       </c>
       <c r="E46" s="3">
+        <v>2826000</v>
+      </c>
+      <c r="F46" s="3">
         <v>3726100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3579700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3354500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3511800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1877800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1943900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1993800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2004600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1827600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1453400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1287300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1367300</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F47" s="3">
         <v>8600</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>24</v>
@@ -2283,8 +2387,8 @@
       <c r="J47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2293,107 +2397,116 @@
         <v>0</v>
       </c>
       <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
         <v>3100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7200</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>657800</v>
+        <v>471500</v>
       </c>
       <c r="E48" s="3">
+        <v>585400</v>
+      </c>
+      <c r="F48" s="3">
         <v>742900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>818800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>843800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>928700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>450900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>467300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>475000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>528700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>786100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>620300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>355200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>407600</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5097100</v>
+        <v>4083500</v>
       </c>
       <c r="E49" s="3">
+        <v>4357200</v>
+      </c>
+      <c r="F49" s="3">
         <v>5987500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8259000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8936900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9735300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4204300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4522700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4567400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4838100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3973700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4294900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3052600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3267500</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>138700</v>
+        <v>170300</v>
       </c>
       <c r="E52" s="3">
+        <v>952300</v>
+      </c>
+      <c r="F52" s="3">
         <v>725700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>174900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>153500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>152700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>54700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>61900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>105900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>131200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>87300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>192500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>93700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>103600</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>9371900</v>
+        <v>8747500</v>
       </c>
       <c r="E54" s="3">
+        <v>9332500</v>
+      </c>
+      <c r="F54" s="3">
         <v>11685400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13259500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13576800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14431600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6630500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7041700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7142000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7502600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4917100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4734100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4793300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5153200</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>435900</v>
+        <v>370700</v>
       </c>
       <c r="E57" s="3">
+        <v>330700</v>
+      </c>
+      <c r="F57" s="3">
         <v>684300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1160700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1010800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1148000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>399200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>436700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>415900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>300800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>177800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>251600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>194300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>180700</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>68500</v>
+        <v>33700</v>
       </c>
       <c r="E58" s="3">
+        <v>67300</v>
+      </c>
+      <c r="F58" s="3">
         <v>76400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>80200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>94400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>93700</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
       <c r="K58" s="3">
-        <v>12500</v>
+        <v>0</v>
       </c>
       <c r="L58" s="3">
         <v>12500</v>
       </c>
       <c r="M58" s="3">
+        <v>12500</v>
+      </c>
+      <c r="N58" s="3">
         <v>9000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>9500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>12300</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>613200</v>
+        <v>540100</v>
       </c>
       <c r="E59" s="3">
+        <v>747600</v>
+      </c>
+      <c r="F59" s="3">
         <v>942800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>518600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>450100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>424000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>145700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>74500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>429400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>371700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>289000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>332300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>344500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>320600</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1409400</v>
+        <v>1229700</v>
       </c>
       <c r="E60" s="3">
+        <v>1405500</v>
+      </c>
+      <c r="F60" s="3">
         <v>2107500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2182500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1953400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2042000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>690600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>723700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>857800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>685100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>475800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>593400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>549600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>513700</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>9394500</v>
+        <v>9352500</v>
       </c>
       <c r="E61" s="3">
+        <v>9382800</v>
+      </c>
+      <c r="F61" s="3">
         <v>9589000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9629600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9637600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9977100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3985900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4369400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4549500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5231100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2659900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2505100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2460000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2550700</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>168400</v>
+        <v>187800</v>
       </c>
       <c r="E62" s="3">
+        <v>216400</v>
+      </c>
+      <c r="F62" s="3">
         <v>238200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>244800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>282500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>286300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>100600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>141300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>340600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>363700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>473700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>934100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>601400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>723700</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>11178600</v>
+        <v>10976300</v>
       </c>
       <c r="E66" s="3">
+        <v>11195100</v>
+      </c>
+      <c r="F66" s="3">
         <v>12131100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12360000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12180000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12595300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4873700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5393800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5747900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6279900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3609400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3646000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3611000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3788100</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,30 +3377,33 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1227300</v>
+      </c>
+      <c r="E70" s="3">
         <v>1162100</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>1100300</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>1056100</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>1041800</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>1000000</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
       <c r="J70" s="3">
         <v>0</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-4953100</v>
+        <v>-5324500</v>
       </c>
       <c r="E72" s="3">
+        <v>-5009000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-3502200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2215300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1752700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1179300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-249800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-396000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-589600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-812400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-741500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-978300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-447700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-252300</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-2968800</v>
+        <v>-3456100</v>
       </c>
       <c r="E76" s="3">
+        <v>-3024700</v>
+      </c>
+      <c r="F76" s="3">
         <v>-1546000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-156600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>355000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>836300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1756800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1647800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1394100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1222700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1307600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1088000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1182300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1365100</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-1450900</v>
+        <v>-315500</v>
       </c>
       <c r="E81" s="3">
+        <v>-1506800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1286900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-462600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-573400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-929500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>140200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>193800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>222800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-70900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>236800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-392400</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>234100</v>
+        <v>134000</v>
       </c>
       <c r="E83" s="3">
-        <v>256100</v>
+        <v>260200</v>
       </c>
       <c r="F83" s="3">
+        <v>296000</v>
+      </c>
+      <c r="G83" s="3">
         <v>276300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>192800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>177700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>92900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>107000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>399100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>303500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>259500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>256600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>262300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>297000</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>289900</v>
+        <v>273100</v>
       </c>
       <c r="E89" s="3">
+        <v>297300</v>
+      </c>
+      <c r="F89" s="3">
         <v>190000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>122300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>436200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>596400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>494100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>586300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>640200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>327100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>289400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>237700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>286100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>131000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-53300</v>
+        <v>-25300</v>
       </c>
       <c r="E91" s="3">
+        <v>-60700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-101300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-131400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-121200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-104100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-82300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-68700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-68300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-56500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-36900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-36800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-28000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-39500</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>38300</v>
+        <v>-57200</v>
       </c>
       <c r="E94" s="3">
+        <v>30900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-82100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-136800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-120200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5154900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-64300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-166200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-54600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3050600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-76000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-63400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-35500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3171500</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,8 +4453,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4257,17 +4490,20 @@
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-538700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-200000</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-83000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-181700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-65000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-139500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-383800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4698600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-409600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-413700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-708400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2578100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>190800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-89700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-299500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2655300</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-5100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-7600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-16000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>19400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-11900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-21000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-21300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2700</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-3800</v>
       </c>
       <c r="P101" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>119500</v>
+      </c>
+      <c r="E102" s="3">
         <v>145700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>37800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-161600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-76300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>140000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>25800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-134700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-166400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>383000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>81900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-52700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-389000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
